--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484647_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484647_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.1304</v>
+        <v>8.9778</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9188</v>
+        <v>7.5341</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2116</v>
+        <v>1.4436</v>
       </c>
       <c r="G2" t="n">
         <v>7.7149</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>1.727</v>
+        <v>0.5744</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5294</v>
+        <v>0.1448</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1976</v>
+        <v>0.4296</v>
       </c>
       <c r="V2" t="n">
         <v>0.3219</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5457</v>
+        <v>5.177</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8531</v>
+        <v>2.757</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6926</v>
+        <v>2.4201</v>
       </c>
       <c r="G3" t="n">
         <v>4.4589</v>
@@ -688,13 +688,13 @@
         <v>2.0158</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4691</v>
+        <v>1.1005</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.6897</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6833</v>
+        <v>0.4108</v>
       </c>
       <c r="V3" t="n">
         <v>1.267</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2048</v>
+        <v>4.9685</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7084</v>
+        <v>4.5712</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4964</v>
+        <v>0.3973</v>
       </c>
       <c r="G4" t="n">
         <v>3.7972</v>
@@ -766,13 +766,13 @@
         <v>0.5498</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1798</v>
+        <v>0.9434</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6026</v>
+        <v>0.4653</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5772</v>
+        <v>0.4781</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3219</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7573</v>
+        <v>3.8896</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6952</v>
+        <v>3.6541</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0621</v>
+        <v>0.2355</v>
       </c>
       <c r="G5" t="n">
         <v>2.956</v>
@@ -844,13 +844,13 @@
         <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1337</v>
+        <v>0.266</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1456</v>
+        <v>0.1045</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0119</v>
+        <v>0.1616</v>
       </c>
       <c r="V5" t="n">
         <v>0.3011</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7397</v>
+        <v>1.8606</v>
       </c>
       <c r="E6" t="n">
-        <v>0.647</v>
+        <v>0.7432</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0927</v>
+        <v>1.1174</v>
       </c>
       <c r="G6" t="n">
         <v>1.0635</v>
@@ -922,13 +922,13 @@
         <v>0.9163</v>
       </c>
       <c r="S6" t="n">
-        <v>0.383</v>
+        <v>0.504</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4201</v>
+        <v>0.5162</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.037</v>
+        <v>-0.0123</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6231</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBAÑEZ</t>
+          <t>J. CARRERAS MUNOZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2753</v>
+        <v>1.5915</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2753</v>
+        <v>-0.7222</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2.3138</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2753</v>
+        <v>1.1618</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6502</v>
+        <v>1.2134</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6251</v>
+        <v>-0.0515</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2753</v>
+        <v>0.8937</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6502</v>
+        <v>1.2013</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6251</v>
+        <v>-0.3076</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.2682</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.0121</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2561</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.0309</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.4272</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.3963</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUNOZ</t>
+          <t>A. ORTEGA IBAÑEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0994</v>
+        <v>1.2753</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0657</v>
+        <v>1.2753</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1651</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1618</v>
+        <v>1.2753</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2134</v>
+        <v>0.6502</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0515</v>
+        <v>0.6251</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8937</v>
+        <v>1.2753</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2013</v>
+        <v>0.6502</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3076</v>
+        <v>0.6251</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2682</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0121</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2561</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5231</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2476</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7181</v>
+        <v>-0.7145</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2306</v>
+        <v>-1.5987</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.8842</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3527</v>
@@ -1234,13 +1234,13 @@
         <v>0.3665</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8156</v>
+        <v>0.188</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6614</v>
+        <v>-0.0294</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1542</v>
+        <v>0.2174</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6412</v>
+        <v>-6.621</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.1924</v>
+        <v>-7.6181</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5512</v>
+        <v>0.9971</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9513</v>
@@ -1312,13 +1312,13 @@
         <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>0.059</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4744</v>
+        <v>0.0487</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4154</v>
+        <v>0.0305</v>
       </c>
       <c r="V11" t="n">
         <v>-1.267</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.2798</v>
+        <v>-8.0162</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.5531</v>
+        <v>-7.2646</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7267</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1327</v>
@@ -1390,13 +1390,13 @@
         <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2406</v>
+        <v>0.5043</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0166</v>
+        <v>0.3051</v>
       </c>
       <c r="U12" t="n">
-        <v>0.224</v>
+        <v>0.1993</v>
       </c>
       <c r="V12" t="n">
         <v>-1.89</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.714</v>
+        <v>13.9891</v>
       </c>
       <c r="E13" t="n">
-        <v>4.656500000000002</v>
+        <v>4.931799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>9.057600000000001</v>
+        <v>9.057499999999999</v>
       </c>
       <c r="G13" t="n">
         <v>20.5914</v>
@@ -1468,13 +1468,13 @@
         <v>11.9117</v>
       </c>
       <c r="S13" t="n">
-        <v>3.853500000000001</v>
+        <v>4.128900000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5424</v>
+        <v>1.8177</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3112</v>
+        <v>2.3113</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5681</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1421</v>
+        <v>5.995</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5596</v>
+        <v>4.9827</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5826</v>
+        <v>1.0124</v>
       </c>
       <c r="G14" t="n">
         <v>4.2943</v>
@@ -1546,13 +1546,13 @@
         <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0598</v>
+        <v>-0.0873</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3643</v>
+        <v>-0.2126</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3045</v>
+        <v>0.1254</v>
       </c>
       <c r="V14" t="n">
         <v>0.3219</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9209</v>
+        <v>3.4895</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1847</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7362</v>
+        <v>2.4971</v>
       </c>
       <c r="G15" t="n">
         <v>0.8776</v>
@@ -1624,13 +1624,13 @@
         <v>1.2828</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5143</v>
+        <v>0.083</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1116</v>
+        <v>-0.3039</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6259</v>
+        <v>0.3869</v>
       </c>
       <c r="V15" t="n">
         <v>1.2461</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5274</v>
+        <v>0.1864</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2539</v>
+        <v>0.0616</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2734</v>
+        <v>0.1248</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9678</v>
@@ -1702,13 +1702,13 @@
         <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2124</v>
+        <v>-0.1286</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1456</v>
+        <v>-0.0467</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0668</v>
+        <v>-0.0818</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4855</v>
+        <v>-1.3223</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8339</v>
+        <v>-2.0262</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3484</v>
+        <v>0.7039</v>
       </c>
       <c r="G17" t="n">
         <v>-2.3027</v>
@@ -1780,13 +1780,13 @@
         <v>1.4661</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6489</v>
+        <v>-0.4857</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1666</v>
+        <v>-0.359</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4822</v>
+        <v>-0.1267</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ROSELLO ORTS</t>
+          <t>J. MARTINEZ PITARCH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6442</v>
+        <v>-1.8237</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9736</v>
+        <v>-0.5232</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6706</v>
+        <v>-1.3005</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.7251</v>
+        <v>-0.8361</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.7055</v>
+        <v>-0.1951</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0196</v>
+        <v>-0.641</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.9239</v>
+        <v>-0.6194</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.0905</v>
+        <v>0.0217</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1667</v>
+        <v>-0.641</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.8012</v>
+        <v>-0.2167</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6149</v>
+        <v>-0.2167</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1863</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3823</v>
+        <v>0.1833</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3823</v>
+        <v>0.1833</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6985</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9503</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2517</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARTINEZ PITARCH</t>
+          <t>V. PRADA SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9198</v>
+        <v>-2.3002</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6194</v>
+        <v>-1.8581</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3005</v>
+        <v>-0.4421</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8361</v>
+        <v>-0.7542</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1951</v>
+        <v>-0.9752999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.641</v>
+        <v>0.2211</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6194</v>
+        <v>1.502</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0217</v>
+        <v>0.7678</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.641</v>
+        <v>0.7342</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2167</v>
+        <v>-2.2563</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2167</v>
+        <v>-1.7431</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.5131</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1833</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1833</v>
+        <v>2.1991</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.3627</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.2997</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.063</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.267</v>
+        <v>-0.6335</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. HERRANDO CUENCA</t>
+          <t>P. ROSELLO ORTS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9568</v>
+        <v>-2.3348</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1048</v>
+        <v>-1.7428</v>
       </c>
       <c r="F20" t="n">
-        <v>0.148</v>
+        <v>-0.592</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.5855</v>
+        <v>-4.7251</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.0949</v>
+        <v>-3.7055</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4905</v>
+        <v>-1.0196</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5473</v>
+        <v>-1.9239</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.3073</v>
+        <v>-2.0905</v>
       </c>
       <c r="L20" t="n">
-        <v>0.76</v>
+        <v>0.1667</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0382</v>
+        <v>-2.8012</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7876</v>
+        <v>-1.6149</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2505</v>
+        <v>-1.1863</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5498</v>
+        <v>2.3823</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>2.3823</v>
       </c>
       <c r="S20" t="n">
-        <v>0.435</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3092</v>
+        <v>0.181</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1258</v>
+        <v>-0.1731</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9658</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. FAJARDO PANOS</t>
+          <t>M. POVEDA CASTELLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8918</v>
+        <v>-2.3729</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5318000000000001</v>
+        <v>-2.2964</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.36</v>
+        <v>-0.0765</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1201</v>
+        <v>-6.1813</v>
       </c>
       <c r="H21" t="n">
-        <v>0.54</v>
+        <v>-2.7481</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4199</v>
+        <v>-3.4332</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1552</v>
+        <v>-3.7402</v>
       </c>
       <c r="K21" t="n">
-        <v>1.062</v>
+        <v>-1.9421</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09320000000000001</v>
+        <v>-1.7981</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0351</v>
+        <v>-2.4412</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.522</v>
+        <v>-0.806</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5131</v>
+        <v>-1.6351</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8326</v>
+        <v>2.5656</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7503</v>
+        <v>-0.4819</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.6029</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0204</v>
+        <v>0.121</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.1778</v>
+        <v>5.3898</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>5.7118</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.1778</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. PRADA SANCHEZ</t>
+          <t>C. FAJARDO PANOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9529</v>
+        <v>-2.3803</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5312</v>
+        <v>-0.2433</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4217</v>
+        <v>-2.137</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7542</v>
+        <v>0.1201</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9752999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2211</v>
+        <v>-0.4199</v>
       </c>
       <c r="J22" t="n">
-        <v>1.502</v>
+        <v>1.1552</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7678</v>
+        <v>1.062</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7342</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2563</v>
+        <v>-1.0351</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.7431</v>
+        <v>-0.522</v>
       </c>
       <c r="O22" t="n">
         <v>-0.5131</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1991</v>
+        <v>1.8326</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0154</v>
+        <v>-0.2389</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9728</v>
+        <v>-0.4823</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0426</v>
+        <v>0.2434</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6335</v>
+        <v>-3.1778</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3219</v>
+        <v>-3.1778</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. POVEDA CASTELLO</t>
+          <t>S. HERRANDO CUENCA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5734</v>
+        <v>-2.388</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1618</v>
+        <v>-2.5856</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4116</v>
+        <v>0.1976</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.1813</v>
+        <v>-3.5855</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.7481</v>
+        <v>-3.0949</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.4332</v>
+        <v>-0.4905</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.7402</v>
+        <v>-1.5473</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9421</v>
+        <v>-2.3073</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.7981</v>
+        <v>0.76</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4412</v>
+        <v>-2.0382</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.806</v>
+        <v>-0.7876</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6351</v>
+        <v>-1.2505</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5656</v>
+        <v>2.3823</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6823</v>
+        <v>0.0038</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.4683</v>
+        <v>-0.1715</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2141</v>
+        <v>0.1753</v>
       </c>
       <c r="V23" t="n">
-        <v>5.3898</v>
+        <v>0.6439</v>
       </c>
       <c r="W23" t="n">
-        <v>5.7118</v>
+        <v>0.9658</v>
       </c>
       <c r="X23" t="n">
         <v>-0.3219</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6771</v>
+        <v>-2.6485</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1299</v>
+        <v>-0.4568</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5472</v>
+        <v>-2.1917</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6776</v>
@@ -2326,13 +2326,13 @@
         <v>1.4661</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1986</v>
+        <v>-0.1701</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8446</v>
+        <v>-0.1715</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.354</v>
+        <v>0.0015</v>
       </c>
       <c r="V24" t="n">
         <v>-1.267</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.2029</v>
+        <v>-3.891</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1694</v>
+        <v>-3.3617</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0334</v>
+        <v>-0.5293</v>
       </c>
       <c r="G25" t="n">
         <v>-3.853</v>
@@ -2404,13 +2404,13 @@
         <v>2.5656</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4781</v>
+        <v>-0.1663</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2542</v>
+        <v>0.0619</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7323</v>
+        <v>-0.2281</v>
       </c>
       <c r="V25" t="n">
         <v>0.3115</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.714</v>
+        <v>-11.7908</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.057600000000001</v>
+        <v>-9.057400000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.6564</v>
+        <v>-2.733299999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-20.5913</v>
@@ -2458,7 +2458,7 @@
         <v>-1.522799999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>2.000900000000001</v>
+        <v>2.0009</v>
       </c>
       <c r="L26" t="n">
         <v>-3.5235</v>
@@ -2467,7 +2467,7 @@
         <v>-19.0686</v>
       </c>
       <c r="N26" t="n">
-        <v>-7.5255</v>
+        <v>-7.525500000000001</v>
       </c>
       <c r="O26" t="n">
         <v>-11.5429</v>
@@ -2482,16 +2482,16 @@
         <v>21.0747</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.8536</v>
+        <v>-1.9306</v>
       </c>
       <c r="T26" t="n">
         <v>-2.311</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.5425</v>
+        <v>0.3807999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>1.567900000000001</v>
+        <v>1.5679</v>
       </c>
       <c r="W26" t="n">
         <v>6.688000000000001</v>
